--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486913_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486913_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6245</v>
+        <v>1.8832</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7814</v>
+        <v>2.0105</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1569</v>
+        <v>-0.1273</v>
       </c>
       <c r="G2" t="n">
         <v>-0.1189</v>
@@ -610,13 +610,13 @@
         <v>1.4374</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5462</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5147</v>
+        <v>0.7437</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0315</v>
+        <v>0.0612</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2402</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. BOIX COLET</t>
+          <t>A. VENTURA PEDREÑO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.2687</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7259</v>
+        <v>-0.6186</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6399</v>
+        <v>0.8873</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.4122</v>
+        <v>-1.6349</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1296</v>
+        <v>-0.7981</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.5418</v>
+        <v>-0.8368</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0779</v>
+        <v>-0.1703</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4862</v>
+        <v>-0.0516</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5916</v>
+        <v>-0.1188</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.4901</v>
+        <v>-1.4646</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3566</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.1335</v>
+        <v>-0.7181</v>
       </c>
       <c r="P3" t="n">
         <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2588</v>
+        <v>-2.0534</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2588</v>
+        <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3196</v>
+        <v>-0.1046</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4879</v>
+        <v>-0.4031</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1683</v>
+        <v>0.2985</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1786</v>
+        <v>2.0082</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4189</v>
+        <v>2.0082</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. FERRER IGLESIA</t>
+          <t>J. BOIX COLET</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1947</v>
+        <v>-0.0137</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1.478</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1947</v>
+        <v>-1.4917</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1947</v>
+        <v>-1.4122</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1947</v>
+        <v>0.1296</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-1.5418</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2.0779</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1.4862</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.5916</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1947</v>
+        <v>-3.4901</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1947</v>
+        <v>-1.3566</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-2.1335</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.2588</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.2199</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.0201</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. VENTURA PEDREÑO</t>
+          <t>N. FERRER IGLESIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2296</v>
+        <v>-0.1947</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9983</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7687</v>
+        <v>-0.1947</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6349</v>
+        <v>-0.1947</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7981</v>
+        <v>-0.1947</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8368</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1703</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0516</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1188</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4646</v>
+        <v>-0.1947</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.1947</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7181</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0534</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6029</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7827</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1799</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>2.0082</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.0082</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1857</v>
+        <v>-0.7237</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7973</v>
+        <v>1.1112</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.983</v>
+        <v>-1.8348</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0648</v>
@@ -922,13 +922,13 @@
         <v>1.2321</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4863</v>
+        <v>-0.0243</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.07770000000000001</v>
+        <v>0.2361</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4087</v>
+        <v>-0.2604</v>
       </c>
       <c r="V6" t="n">
         <v>1.4189</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9768</v>
+        <v>-1.6177</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0726</v>
+        <v>-1.6542</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0958</v>
+        <v>0.0365</v>
       </c>
       <c r="G7" t="n">
         <v>-1.329</v>
@@ -1000,13 +1000,13 @@
         <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2371</v>
+        <v>0.122</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3875</v>
+        <v>0.0309</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1504</v>
+        <v>0.0911</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CASTILLO CARRASCO</t>
+          <t>F. GARRIDO TEBAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3268</v>
+        <v>-2.2259</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5033</v>
+        <v>-2.7557</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8235</v>
+        <v>0.5298</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5787</v>
+        <v>-3.0879</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3787</v>
+        <v>-0.5356</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2</v>
+        <v>-2.5522</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7318</v>
+        <v>-1.8179</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2974</v>
+        <v>0.1557</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5656</v>
+        <v>-1.9737</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8468</v>
+        <v>-1.2699</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0813</v>
+        <v>-0.6913</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.5786</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4107</v>
+        <v>1.8481</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2251</v>
+        <v>0.2809</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4339</v>
+        <v>0.089</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2088</v>
+        <v>0.1919</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. GARRIDO TEBAN</t>
+          <t>J. CASTILLO CARRASCO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5463</v>
+        <v>-2.611</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1354</v>
+        <v>-0.8171</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5891</v>
+        <v>-1.7939</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.0879</v>
+        <v>-1.5787</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5356</v>
+        <v>-1.3787</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.5522</v>
+        <v>-0.2</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8179</v>
+        <v>-0.7318</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1557</v>
+        <v>-1.2974</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9737</v>
+        <v>0.5656</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2699</v>
+        <v>-0.8468</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6913</v>
+        <v>-0.0813</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5786</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8481</v>
+        <v>0.4107</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0395</v>
+        <v>-0.0591</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2907</v>
+        <v>0.1201</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2512</v>
+        <v>-0.1791</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7557</v>
+        <v>-2.8603</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4982</v>
+        <v>-1.6028</v>
       </c>
       <c r="F10" t="n">
         <v>-1.2575</v>
@@ -1234,10 +1234,10 @@
         <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2944</v>
+        <v>0.1898</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0541</v>
+        <v>-0.0505</v>
       </c>
       <c r="U10" t="n">
         <v>0.2403</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5951</v>
+        <v>-3.456</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3856</v>
+        <v>-2.4243</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2096</v>
+        <v>-1.0317</v>
       </c>
       <c r="G11" t="n">
         <v>-5.3417</v>
@@ -1312,13 +1312,13 @@
         <v>2.0534</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5679</v>
+        <v>0.707</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6274</v>
+        <v>0.5887</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0595</v>
+        <v>0.1183</v>
       </c>
       <c r="V11" t="n">
         <v>1.1786</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6463</v>
+        <v>-3.8661</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1416</v>
+        <v>-1.8278</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5047</v>
+        <v>-2.0383</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4496</v>
@@ -1390,13 +1390,13 @@
         <v>0.8214</v>
       </c>
       <c r="S12" t="n">
-        <v>0.214</v>
+        <v>-0.0058</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3798</v>
+        <v>-0.066</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5937</v>
+        <v>0.0602</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.7465</v>
+        <v>-15.4172</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.430400000000001</v>
+        <v>-7.1008</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.3162</v>
+        <v>-8.3163</v>
       </c>
       <c r="G13" t="n">
         <v>-18.3118</v>
@@ -1441,7 +1441,7 @@
         <v>-12.1959</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4917</v>
+        <v>2.491700000000001</v>
       </c>
       <c r="K13" t="n">
         <v>4.1389</v>
@@ -1468,13 +1468,13 @@
         <v>14.374</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8014</v>
+        <v>2.1307</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1996</v>
+        <v>1.5289</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6017</v>
+        <v>0.6019</v>
       </c>
       <c r="V13" t="n">
         <v>1.7906</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.5039</v>
+        <v>8.947100000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5861</v>
+        <v>4.0171</v>
       </c>
       <c r="F14" t="n">
-        <v>4.9178</v>
+        <v>4.93</v>
       </c>
       <c r="G14" t="n">
         <v>4.248</v>
@@ -1546,13 +1546,13 @@
         <v>2.2588</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0732</v>
+        <v>0.5163</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1384</v>
+        <v>0.5694</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0531</v>
       </c>
       <c r="V14" t="n">
         <v>2.3347</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9904</v>
+        <v>6.8848</v>
       </c>
       <c r="E15" t="n">
-        <v>5.5827</v>
+        <v>5.7919</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4077</v>
+        <v>1.0929</v>
       </c>
       <c r="G15" t="n">
         <v>6.6576</v>
@@ -1624,13 +1624,13 @@
         <v>2.8748</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.275</v>
+        <v>-0.3806</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5542</v>
+        <v>-0.345</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7208</v>
+        <v>-0.0356</v>
       </c>
       <c r="V15" t="n">
         <v>-0.8295</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.115</v>
+        <v>4.0721</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8543</v>
+        <v>3.482</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2606</v>
+        <v>0.5901</v>
       </c>
       <c r="G16" t="n">
         <v>2.9115</v>
@@ -1702,13 +1702,13 @@
         <v>2.0534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9116</v>
+        <v>0.0455</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9804</v>
+        <v>-0.3527</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0688</v>
+        <v>0.3983</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9384</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0304</v>
+        <v>2.8707</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7924</v>
+        <v>2.3154</v>
       </c>
       <c r="F17" t="n">
-        <v>0.238</v>
+        <v>0.5554</v>
       </c>
       <c r="G17" t="n">
         <v>3.8607</v>
@@ -1780,13 +1780,13 @@
         <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.974</v>
+        <v>-0.1337</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5851</v>
+        <v>-0.0621</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3889</v>
+        <v>-0.0716</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2402</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8176</v>
+        <v>2.0721</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1957</v>
+        <v>0.1181</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0133</v>
+        <v>1.954</v>
       </c>
       <c r="G18" t="n">
         <v>2.3771</v>
@@ -1858,13 +1858,13 @@
         <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4075</v>
+        <v>-0.153</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5192</v>
+        <v>-0.2054</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1117</v>
+        <v>0.0524</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1786</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4598</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.593</v>
+        <v>-1.8022</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1332</v>
+        <v>1.0739</v>
       </c>
       <c r="G19" t="n">
         <v>0.7536</v>
@@ -1936,13 +1936,13 @@
         <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>0.224</v>
+        <v>-0.0445</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3021</v>
+        <v>0.0929</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.1374</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8272</v>
+        <v>-1.1926</v>
       </c>
       <c r="E20" t="n">
         <v>-1.5345</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2927</v>
+        <v>0.3419</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8245</v>
@@ -2014,13 +2014,13 @@
         <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0376</v>
+        <v>-0.403</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2249</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8128</v>
+        <v>-0.1781</v>
       </c>
       <c r="V20" t="n">
         <v>0.2402</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0698</v>
+        <v>-1.8868</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8018</v>
+        <v>-1.5926</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2679</v>
+        <v>-0.2942</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5751</v>
@@ -2092,13 +2092,13 @@
         <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4786</v>
+        <v>0.6616</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1513</v>
+        <v>0.0579</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6298</v>
+        <v>0.6036</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1786</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3539</v>
+        <v>-3.2005</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3743</v>
+        <v>-2.4789</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9797</v>
+        <v>-0.7216</v>
       </c>
       <c r="G22" t="n">
         <v>-0.09710000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>0.8214</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0286</v>
+        <v>0.1821</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0272</v>
+        <v>-0.1318</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0559</v>
+        <v>0.3139</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>15.7466</v>
+        <v>17.8386</v>
       </c>
       <c r="E23" t="n">
-        <v>8.3162</v>
+        <v>8.316300000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>7.4303</v>
+        <v>9.522399999999999</v>
       </c>
       <c r="G23" t="n">
         <v>18.3118</v>
@@ -2248,13 +2248,13 @@
         <v>15.4007</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8013</v>
+        <v>0.2906999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6018000000000002</v>
+        <v>-0.6016999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1997</v>
+        <v>0.8924000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7904</v>
